--- a/CV_RTR26.xlsx
+++ b/CV_RTR26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Girija Kulkarni\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ROBOCON2026\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB003E39-4D91-4646-9952-D6532AE4D948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2960579-67FA-4C10-A92A-E56384CB3F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1DA5ACE8-DE1A-44C0-A696-CBF2F77725EA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t xml:space="preserve">Month </t>
   </si>
@@ -109,6 +109,34 @@
   </si>
   <si>
     <t>but facing issues to recognise multiple in one frame and also issues with blue bg</t>
+  </si>
+  <si>
+    <t>yolov8n.pt</t>
+  </si>
+  <si>
+    <t>Not proper blob detection worked due to Realtime RGB inference. Furthermore, the format conversions of yolo8 model did not work for ReCamera as and did not support working of realtime working of yolo8 model on camera despite trying through ssh and cpp based files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trained models based on grayscale, only Symbol detection, Worked on LED based blob detection using cv, tried yolov8 model convesion </t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Led accuracy &gt; 98%, overfitting accuracy and precision models with higher class loss scores and box loss scores. Model conversion failed despite following Recamera Documentation and executable file generation in WSL . Executable cpp file for imape recognition was transferred via ssh and failed to launch on Recamera Terminal.
+Switched to Logitech C270 camera along with Raspi-4, as it support all yolo models and better realtime cv python script support.</t>
+  </si>
+  <si>
+    <t>Shifted to Yolo26 due to lower dfl loss score and overall better data pattern retention and better accuracy and precision than that of yolov8</t>
+  </si>
+  <si>
+    <t>Refined the Dataset to just 5 thousand images with Arena backgrounds, Empty backgrounds and also multiple symbols in one frame. Shifted to Yolo26 from yolov8. Implemented primary coordinates detection od the KFS via I2C based on this trained model</t>
+  </si>
+  <si>
+    <t>yolo26n.pt, yolo26s.pt</t>
+  </si>
+  <si>
+    <t>Accuracy of the yolo26 model ~95-96%. Better recognition in real time using grayscale. Realtime exposure adjustment possible via the python script supported on Raspi. I2C can give pixel values of center coordinates of Real detected KFS from the frame of 640 x 480. FPS is approximately 6.</t>
   </si>
 </sst>
 </file>
@@ -165,17 +193,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,110 +524,128 @@
     <col min="1" max="1" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="33.453125" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="120.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:5" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="1"/>
+    <row r="7" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
